--- a/Java24 HuuThanh Database Design.xlsx
+++ b/Java24 HuuThanh Database Design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java24\3.Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82422C1-C8E0-499B-95FA-FDA1E3D01E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC844C4D-9884-4C0D-961E-F96CCF5F89AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,16 +25,151 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
     <t>MatHang</t>
+  </si>
+  <si>
+    <t>MaMH</t>
+  </si>
+  <si>
+    <t>TenMH</t>
+  </si>
+  <si>
+    <t>KichThuoc(s)</t>
+  </si>
+  <si>
+    <t>GiaBan</t>
+  </si>
+  <si>
+    <t>GiaMua</t>
+  </si>
+  <si>
+    <t>ChatLieu(s)</t>
+  </si>
+  <si>
+    <t>MauSac(s)</t>
+  </si>
+  <si>
+    <t>HinhAnh</t>
+  </si>
+  <si>
+    <t>DonHang</t>
+  </si>
+  <si>
+    <t>MaDH</t>
+  </si>
+  <si>
+    <t>MaKH</t>
+  </si>
+  <si>
+    <t>NgayDatHang</t>
+  </si>
+  <si>
+    <t>TongSoLuong</t>
+  </si>
+  <si>
+    <t>TongTien</t>
+  </si>
+  <si>
+    <t>PhiVanChuyen</t>
+  </si>
+  <si>
+    <t>PhuongThucThanhToan</t>
+  </si>
+  <si>
+    <t>DiaChi</t>
+  </si>
+  <si>
+    <t>SoDienThoai</t>
+  </si>
+  <si>
+    <t>TrangThaiDH</t>
+  </si>
+  <si>
+    <t>HoTen</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>KhachHang</t>
+  </si>
+  <si>
+    <t>MaLoai</t>
+  </si>
+  <si>
+    <t>TenLoai</t>
+  </si>
+  <si>
+    <t>ChiTietDonHang</t>
+  </si>
+  <si>
+    <t>LoaiHang</t>
+  </si>
+  <si>
+    <t>TaiKhoan</t>
+  </si>
+  <si>
+    <t>MaTK</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>SoLuong</t>
+  </si>
+  <si>
+    <t>MauSac</t>
+  </si>
+  <si>
+    <t>SoLuongTon</t>
+  </si>
+  <si>
+    <t>NhaSanXuat</t>
+  </si>
+  <si>
+    <t>MaCTDH</t>
+  </si>
+  <si>
+    <t>DonGia</t>
+  </si>
+  <si>
+    <t>NhanVien</t>
+  </si>
+  <si>
+    <t>VaiTro</t>
+  </si>
+  <si>
+    <t>LichSuDonHang</t>
+  </si>
+  <si>
+    <t>MaLSDH</t>
+  </si>
+  <si>
+    <t>MaDonHang</t>
+  </si>
+  <si>
+    <t>TrangThai</t>
+  </si>
+  <si>
+    <t>NgayCapNhat</t>
+  </si>
+  <si>
+    <t>MaNV</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>THIẾT KẾ DATABASE - WEBSITE QUẢN LÝ CỬA HÀNG THỜI TRANG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,7 +196,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -69,8 +203,17 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -83,8 +226,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -107,15 +256,62 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -396,170 +592,290 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:M29"/>
-  <sheetFormatPr defaultColWidth="24.625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:M29"/>
+  <sheetFormatPr defaultColWidth="26.625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="24.625" style="1"/>
+    <col min="1" max="16384" width="26.625" style="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="10"/>
+    </row>
     <row r="3" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
     </row>
     <row r="4" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
     </row>
     <row r="5" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
     </row>
     <row r="7" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
     </row>
     <row r="8" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="5"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="5"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
     </row>
     <row r="11" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="5"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
     </row>
     <row r="12" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="5"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
     </row>
     <row r="13" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="5"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
     </row>
     <row r="14" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -567,222 +883,225 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
     </row>
     <row r="15" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
     </row>
     <row r="16" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
     </row>
     <row r="17" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
     </row>
     <row r="18" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
     </row>
     <row r="19" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
     </row>
     <row r="20" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
     </row>
     <row r="21" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
     </row>
     <row r="22" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
     </row>
     <row r="23" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
     </row>
     <row r="24" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
     </row>
     <row r="25" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
     </row>
     <row r="26" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
     </row>
     <row r="27" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
     </row>
     <row r="28" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
     </row>
     <row r="29" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
